--- a/artfynd/A 30670-2026 artfynd.xlsx
+++ b/artfynd/A 30670-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058949</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058944</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058946</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1106,6 +1126,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134850226</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058945</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1318,6 +1348,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058942</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1424,6 +1459,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058948</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1530,6 +1570,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058953</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058950</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,8 +1792,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135058943</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30670-2026 artfynd.xlsx
+++ b/artfynd/A 30670-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135058949</v>
       </c>
       <c r="B2" t="n">
-        <v>101301</v>
+        <v>101349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135058944</v>
       </c>
       <c r="B3" t="n">
-        <v>103776</v>
+        <v>103827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135058946</v>
       </c>
       <c r="B4" t="n">
-        <v>103776</v>
+        <v>103827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>135058945</v>
       </c>
       <c r="B6" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135058942</v>
       </c>
       <c r="B7" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135058948</v>
       </c>
       <c r="B8" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>135058953</v>
       </c>
       <c r="B9" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>135058950</v>
       </c>
       <c r="B10" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135058943</v>
       </c>
       <c r="B11" t="n">
-        <v>101940</v>
+        <v>101988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 30670-2026 artfynd.xlsx
+++ b/artfynd/A 30670-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135058949</v>
       </c>
       <c r="B2" t="n">
-        <v>101349</v>
+        <v>101376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>135058944</v>
       </c>
       <c r="B3" t="n">
-        <v>103827</v>
+        <v>103854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>135058946</v>
       </c>
       <c r="B4" t="n">
-        <v>103827</v>
+        <v>103854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>135058945</v>
       </c>
       <c r="B6" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>135058942</v>
       </c>
       <c r="B7" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,7 +1359,7 @@
         <v>135058948</v>
       </c>
       <c r="B8" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>135058953</v>
       </c>
       <c r="B9" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
         <v>135058950</v>
       </c>
       <c r="B10" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,7 +1692,7 @@
         <v>135058943</v>
       </c>
       <c r="B11" t="n">
-        <v>101988</v>
+        <v>102015</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
